--- a/DATA/MODELADO/Diagnosticos/Exp04/diagnostico_modelo_Exp04.xlsx
+++ b/DATA/MODELADO/Diagnosticos/Exp04/diagnostico_modelo_Exp04.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,29 +448,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Accuracy</t>
+          <t>MAE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.9487</t>
+          <t>0.2454</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítico</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Precision</t>
+          <t>RMSE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>0.2723</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -482,85 +482,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Recall</t>
+          <t>MAPE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6364</t>
+          <t>24.54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítico</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F1 Score</t>
+          <t>R²</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7778</t>
+          <t>0.3880</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aceptable</t>
+          <t>Crítico</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Especificidad</t>
+          <t>Estado General</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>Aceptable</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Excelente</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Accuracy Balanceada</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>0.82</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Estado General</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>MODELO APROBADO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
+          <t>Crítico</t>
         </is>
       </c>
     </row>
